--- a/Excel/Aula 05/ZAP.xlsx
+++ b/Excel/Aula 05/ZAP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tosenac-my.sharepoint.com/personal/jaderson_gpi_to_senac_br/Documents/Excel Avançado/Aula 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno\Documents\GitHub\Jaderson-Araujo\Excel\Aula 05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{8DB9AC5C-2A2E-4F1F-A42C-9F1FF281CF82}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{3C7281BA-69EF-471F-BF63-D172423B8055}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5E253C-F3A8-4B02-9869-3B1A45106B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RELATORIO" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,17 @@
     <sheet name="Função" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -181,7 +192,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -312,9 +323,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -352,9 +363,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -387,26 +398,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -439,26 +433,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -633,18 +610,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.109375" customWidth="1"/>
-    <col min="2" max="2" width="20.109375" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="17.5546875" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -655,7 +632,7 @@
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
     </row>
-    <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>14</v>
       </c>
@@ -666,7 +643,7 @@
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
@@ -677,7 +654,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>1</v>
       </c>
@@ -701,7 +678,7 @@
       </c>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>8</v>
       </c>
@@ -717,10 +694,16 @@
       <c r="E6" s="9">
         <v>6</v>
       </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F6" s="10">
+        <f>NETWORKDAYS.INTL(C6,D6,11,FERIADOS!A:A)</f>
+        <v>47</v>
+      </c>
+      <c r="G6" s="11">
+        <f>E6*F6*B$3</f>
+        <v>15510</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>9</v>
       </c>
@@ -736,10 +719,16 @@
       <c r="E7" s="9">
         <v>6</v>
       </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F7" s="10">
+        <f>NETWORKDAYS.INTL(C7,D7,11,FERIADOS!A:A)</f>
+        <v>28</v>
+      </c>
+      <c r="G7" s="11">
+        <f t="shared" ref="G7:G16" si="0">E7*F7*B$3</f>
+        <v>9240</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>10</v>
       </c>
@@ -755,10 +744,16 @@
       <c r="E8" s="9">
         <v>8</v>
       </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F8" s="10">
+        <f>NETWORKDAYS.INTL(C8,D8,11,FERIADOS!A:A)</f>
+        <v>32</v>
+      </c>
+      <c r="G8" s="11">
+        <f t="shared" si="0"/>
+        <v>14080</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>9</v>
       </c>
@@ -774,10 +769,16 @@
       <c r="E9" s="9">
         <v>4</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F9" s="10">
+        <f>NETWORKDAYS.INTL(C9,D9,11,FERIADOS!A:A)</f>
+        <v>22</v>
+      </c>
+      <c r="G9" s="11">
+        <f t="shared" si="0"/>
+        <v>4840</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>10</v>
       </c>
@@ -793,10 +794,16 @@
       <c r="E10" s="9">
         <v>4</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F10" s="10">
+        <f>NETWORKDAYS.INTL(C10,D10,11,FERIADOS!A:A)</f>
+        <v>24</v>
+      </c>
+      <c r="G10" s="11">
+        <f t="shared" si="0"/>
+        <v>5280</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>8</v>
       </c>
@@ -812,10 +819,16 @@
       <c r="E11" s="9">
         <v>6</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F11" s="10">
+        <f>NETWORKDAYS.INTL(C11,D11,11,FERIADOS!A:A)</f>
+        <v>7</v>
+      </c>
+      <c r="G11" s="11">
+        <f t="shared" si="0"/>
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>8</v>
       </c>
@@ -831,10 +844,16 @@
       <c r="E12" s="9">
         <v>8</v>
       </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="11"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F12" s="10">
+        <f>NETWORKDAYS.INTL(C12,D12,11,FERIADOS!A:A)</f>
+        <v>17</v>
+      </c>
+      <c r="G12" s="11">
+        <f t="shared" si="0"/>
+        <v>7480</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>10</v>
       </c>
@@ -850,10 +869,16 @@
       <c r="E13" s="9">
         <v>6</v>
       </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="11"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F13" s="10">
+        <f>NETWORKDAYS.INTL(C13,D13,11,FERIADOS!A:A)</f>
+        <v>23</v>
+      </c>
+      <c r="G13" s="11">
+        <f t="shared" si="0"/>
+        <v>7590</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>9</v>
       </c>
@@ -869,10 +894,16 @@
       <c r="E14" s="9">
         <v>4</v>
       </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="11"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F14" s="10">
+        <f>NETWORKDAYS.INTL(C14,D14,11,FERIADOS!A:A)</f>
+        <v>11</v>
+      </c>
+      <c r="G14" s="11">
+        <f t="shared" si="0"/>
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>10</v>
       </c>
@@ -888,10 +919,16 @@
       <c r="E15" s="9">
         <v>4</v>
       </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="11"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F15" s="10">
+        <f>NETWORKDAYS.INTL(C15,D15,11,FERIADOS!A:A)</f>
+        <v>12</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" si="0"/>
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>8</v>
       </c>
@@ -907,10 +944,16 @@
       <c r="E16" s="9">
         <v>8</v>
       </c>
-      <c r="F16" s="10"/>
-      <c r="G16" s="11"/>
-    </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="F16" s="10">
+        <f>NETWORKDAYS.INTL(C16,D16,11,FERIADOS!A:A)</f>
+        <v>15</v>
+      </c>
+      <c r="G16" s="11">
+        <f t="shared" si="0"/>
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="19" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
@@ -927,47 +970,47 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
         <v>41275</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>41299</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>41317</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>41362</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>41385</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>41395</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>41424</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>40733</v>
       </c>
@@ -980,7 +1023,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
